--- a/Arquivos_RBN/dados_acareacoes_RBN.xlsx
+++ b/Arquivos_RBN/dados_acareacoes_RBN.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3320099470499</t>
+          <t>6052726271491</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(RBN LOC) VAGLIDOM NAPOLEON</t>
+          <t>(RBN INT)RODRIGO OLIMPIO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,44 +481,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Emanuelle Victoria Gonçalves costa</t>
+          <t>BRENDA GOMES COSTA SOUSA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+5531999250723</t>
+          <t>+5531997087594</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Alameda dos Rubis 771 Casa, Ribeirão das Neves</t>
+          <t>RUA ONZE, Esmeraldas</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kit 3 1 Top Tube Modelagem Acinturada Cropped Básico*1</t>
+          <t>DIVERSOS*1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-08 11:53:27</t>
+          <t>2026-06-09 16:09:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6052726801775</t>
+          <t>3320006515384</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(RBN INT)RODRIGO OLIMPIO</t>
+          <t>( RBN-ESMERALDAS) GILSINEI FERREIRA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,39 +528,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Arilaine Pereira</t>
+          <t>ingrid katlyn</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+5531993241372</t>
+          <t>+5531971599806</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rua Sete 141 Casa, Esmeraldas</t>
+          <t>Rua 8 75 casa, Esmeraldas</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Casaco Tecido Feminino*1+Terno feminino de poliéster*1</t>
+          <t>Coloração Permanente Preto Azulado 1.1 50g - Kamaleão Color*1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>342.83</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-08 11:07:17</t>
+          <t>2026-06-09 13:26:46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3320081478531</t>
+          <t>3320099470499</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -575,44 +575,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>William e Eliza</t>
+          <t>Emanuelle Victoria Gonçalves costa</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+5531997370516</t>
+          <t>+5531999250723</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rua José Soares da Silva 117, Ribeirão das Neves</t>
+          <t>Alameda dos Rubis 771 Casa, Ribeirão das Neves</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kit 5 Bodysplash Masculinos Famosos Perfumes Arabes Spray 60ml*1</t>
+          <t>Kit 3 1 Top Tube Modelagem Acinturada Cropped Básico*1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-06-05 12:48:31</t>
+          <t>2026-06-08 11:53:27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3320005492387</t>
+          <t>6052726801775</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(RBN LOC) VAGLIDOM NAPOLEON</t>
+          <t>(RBN INT)RODRIGO OLIMPIO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -622,79 +622,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>marinafernanda721</t>
+          <t>Arilaine Pereira</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+5531983885243</t>
+          <t>+5531993241372</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rua Cristalina 81 casa, Ribeirão das Neves</t>
+          <t>Rua Sete 141 Casa, Esmeraldas</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jaqueta De Couro Feminina Com Ziper e Botão*1</t>
+          <t>Casaco Tecido Feminino*1+Terno feminino de poliéster*1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>49.99</t>
+          <t>342.83</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-06-05 12:47:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3320022486049</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>(RBN INT) ELTON LOPES DA SILVA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Fake Delivery</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>camilla</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>+5531998936702</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>rua Benedito Quintino 376 supermercado do Zé abelha, Jaboticatubas</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Choker Cruz Country Feminina Dupla Camurça Ajustável Pingente Grande Dourado Prata Rodeio*1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-05 12:46:05</t>
+          <t>2026-06-08 11:07:17</t>
         </is>
       </c>
     </row>

--- a/Arquivos_RBN/dados_acareacoes_RBN.xlsx
+++ b/Arquivos_RBN/dados_acareacoes_RBN.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,59 +466,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6052726271491</t>
+          <t>3320024589001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(RBN INT)RODRIGO OLIMPIO</t>
+          <t>(RBN LOC) Isaque Amaro</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fake Delivery</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BRENDA GOMES COSTA SOUSA</t>
+          <t>Thayler Victor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+5531997087594</t>
+          <t>+5531981104689</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>RUA ONZE, Esmeraldas</t>
+          <t>Rua Maria Angelina Gomes 55, Ribeirão das Neves</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIVERSOS*1</t>
+          <t>Mini Massageador Elétrico Portátil EMS Para Pescoço e Corpo Relaxante*1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>11.87</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-09 16:09:42</t>
+          <t>2026-07-16 14:36:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3320006515384</t>
+          <t>3320025417163</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>( RBN-ESMERALDAS) GILSINEI FERREIRA</t>
+          <t>(RBN INT) ALVARO LUIZ BARBOSA (CONFINS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,44 +528,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ingrid katlyn</t>
+          <t>Helena de jesus domingos</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+5531971599806</t>
+          <t>+5531985081487</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rua 8 75 casa, Esmeraldas</t>
+          <t>rua Antônio de Souza 48 casa, São José da Lapa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coloração Permanente Preto Azulado 1.1 50g - Kamaleão Color*1</t>
+          <t>Panela De Pressão MTA 4,5 Litros Antiaderente Com Visor De Vidro Temperado E Fechamento Interno Original NF*3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>384.23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-09 13:26:46</t>
+          <t>2026-07-16 13:08:25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3320099470499</t>
+          <t>3320004566701</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(RBN LOC) VAGLIDOM NAPOLEON</t>
+          <t>(RBN LOC) PEDRO HENRIQUE DINIZA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -575,39 +575,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Emanuelle Victoria Gonçalves costa</t>
+          <t>Carlos Isidorio de Andrade</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+5531999250723</t>
+          <t>+5531988324158</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Alameda dos Rubis 771 Casa, Ribeirão das Neves</t>
+          <t>avenida Elvis Aron Presley 54 casa, Ribeirão das Neves</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kit 3 1 Top Tube Modelagem Acinturada Cropped Básico*1</t>
+          <t>Jogo Kit 50 Brocas Aço Rapido 1mm 1,5mm 2mm 2,5mm 3mm (50pç)*1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-06-08 11:53:27</t>
+          <t>2026-07-16 11:21:43</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6052726801775</t>
+          <t>3320098652495</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,32 +622,1113 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Arilaine Pereira</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+5531993241372</t>
+          <t>+5553193892580</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rua Sete 141 Casa, Esmeraldas</t>
+          <t>Rua Xingus 49 casa, Esmeraldas</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Casaco Tecido Feminino*1+Terno feminino de poliéster*1</t>
+          <t>Body Spray Club 6 100ml- Eudora*1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>342.83</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-06-08 11:07:17</t>
+          <t>2026-07-16 11:21:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3320013661257</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>(RBN INT)RODRIGO OLIMPIO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+5553193892580</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rua Xingus 49 casa, Esmeraldas</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Capinha Capa de silicone Anti-impacto silicone Resistente A Choques simplicidade para iPhone 7 8 X XR XS 11 12 13 14 15 16 pro max plus case*1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-07-16 11:20:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3320070650067</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>(RBN LOC) VINICIUS PASSOS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>brubru</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+5531975572832</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rua Antônio Miguel Cerqueira Neto 618 MY PASS, Ribeirão das Neves</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Truss Uso Obrigatório Reconstrução Capilar Spray Leave in 260ml - Tratamento Poderoso para Todos os Tipos de Cabelo*1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>82.89</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:46:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3320043658448</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>(RBN INT)RODRIGO OLIMPIO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>wesleywanderley de Oliveira</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>+5531990763023</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rua Argentina 17 casa, Esmeraldas</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PENDRIVE 16 GB 2000 M*1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:46:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3320022660481</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>( RBN INT) GILSINEI FERREIRA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kley Oliveira</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>+5531983158810</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rua Tapajós 225 Casa, Esmeraldas</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Intercomunicador Fone de Ouvido Bluetooth para Capacete Moto com RGB e Microfone*1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:46:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3320041662050</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>( RBN INT) GILSINEI FERREIRA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Anônimo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>+5531999233659</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beco Senhora Aparecida 13, Ribeirão das Neves</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Intercomunicador Fone de Ouvido Bluetooth para Capacete Moto com RGB e Microfone*1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:45:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3320047649519</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>(RBN INT)RODRIGO OLIMPIO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Reginaldo Santana Gomes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+5531997158768</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rua Quinze 39 casa, Esmeraldas</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cinto masculino couro social Com Fivela Modelo Catraca Metal Automatica qualidade superior*2</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-07-15 14:35:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3320021613279</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>(RBN INT) FRANCISCO ANTONIO NUNES</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Maria Aparecida Alves Ferreira</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>+5531993345768</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>rua Ilda Fonseca 20 casa, Jaboticatubas</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Maycrene - Linha Tutano de Boi + D-Pantenol e Queratina - Blindagem para Cabelos Frascos e com Queda*2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-07-15 14:35:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3320054650669</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(RBN LOC) WESLEY SOARES DE FARIA(NEVES)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Arthur L</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>+5531994618725</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>R. Moacir Menezes - Sevilha (1 Seção)33860-112 2000 2000 bloco 5 ,102, Ribeirão das Neves</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Atualizado Projetor Smart HY 320 Android Full HD 1920x1080 Bluetooth Wi-fi*1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-07-15 14:34:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3320079664802</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>(RBN LOC) Isaque Amaro</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Michele Magalhães Fr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>+5531995926791</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Avenida Oswaldo Alves Araújo 935 casa, Ribeirão das Neves</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>calça de poliester*2</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-07-15 14:32:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3320054665207</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>( RBN INT) GILSINEI FERREIRA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Clarinha</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>+5531994768033</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rua Porteirinha 206 casa portao cinza, Esmeraldas</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Amor e Outras Conspirações Para amar tem que acreditar uma websérie sobre criptídeos e fantasma - Mallory Marlowe, Editora Intrínseca*1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-07-15 12:35:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3320041662131</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>( RBN INT) GILSINEI FERREIRA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>sarah lais</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>+5531971424211</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rua Dez 200 Casa, portão preto, Esmeraldas</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Bota Feminina Texana Western Que Está Bombando no TikTok Aproveite*1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-07-15 12:35:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3320095659985</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>(RBN LOC) Isaque Amaro</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Talita Kese Silva Ci</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>+5531975294523</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rua Maria Adelaide 1160 portao marrom de garagem, Ribeirão das Neves</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Kit 4 Pares De Meias Antiderrapante Sapatilha Pares Menino/menina*1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:42:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3320092611782</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>(RBN INT) MILEIDE BERTOLDO LOPES</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>glazieleteixeira</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>+5531992044100</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rod.Mg 424 Km 06 865 Galpão Auto Center, São José da Lapa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lixeira Inteligente Automática 12L Com Sensor Para Cozinha Sala Banheiro E Escritório*1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4.69</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3320029627877</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>(RBN INT) MILEIDE BERTOLDO LOPES</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>glazieleteixeira</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>+5531992044100</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rod.Mg 424 Km 06 865 Galpão Auto Center, São José da Lapa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Luminária de Mesa Cristal LED Recarregável 3 Tons Abajur de Cabeceira para Quarto e Sala Decoração*1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5.59</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3320019651052</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>(RBN INT)RODRIGO OLIMPIO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Kelly Silva</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>+5531997266182</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rua Venezuela 248 casa 3, Esmeraldas</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nebulizador/Inalador Ultrassônico Portátil Usb Bivolt Adulto E Infantil*1</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>38.59</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:41:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3320085646023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>( RBN INT) GILSINEI FERREIRA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Andreza Fernandes</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>+5531973497628</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Alameda dos Lagos 7 casa, Esmeraldas</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Babuche Infantil Menina Menino Confortável Lançamento Passeio*1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:40:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3320033662778</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>( RBN INT) GILSINEI FERREIRA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>edercorretordeimoveis</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>+5531997681326</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>rua oito 515 casa, Esmeraldas</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porta Chaves Organizador Parede Decorativo Preto Moderno Ganchos Decoração Multiuso Carteira*1</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>21.39</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:40:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3320085635717</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>(RBN LOC) RAPHAEL PASSOS AVELAR</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>prisley</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>+5531991753384</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rua Sérgio de Souza Nascimento 176 casa, Ribeirão das Neves</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Estrela, redondo, quadrado, coração – piercings para nariz e orelha com zircônia de 3 mm em aço inoxidável.*1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:40:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3320096651261</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>(RBN LOC) VAGLIDOM NAPOLEON</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Vinícius</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>+5531995591018</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rua Treze 132 Em frente a o crás, Ribeirão das Neves</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>LDK Kit 3 Body Infantil Verão Meia Malha Manga Curta 100% Algodão Confortável e Respirável Unissex Feminino Masculino Branco Amarelo Mescla Rosa Azul*1</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>27.89</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:40:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3320001666544</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>( RBN INT) GILSINEI FERREIRA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Dany Oliveira</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>+5531993259963</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rua Três 99 casa, Esmeraldas</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Kit 2 Tênis Feminino Casual Confortável Branco Preto*1</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>18.84</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:40:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3320041669825</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>(RBN LOC) VAGLIDOM NAPOLEON</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Victor Hugo</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>+5553186964188</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rua Vinte e Um 420 casa, Ribeirão das Neves</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Conjunto Camiseta Blessed 100% Algodão + Short Tactel Preto*1</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:39:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3320080654690</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>(RBN INT) HENRIQUE JUNIO DO S NEVES(ESM)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sarah</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>+5531999751320</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Avenida Palmeiras 375 Casa, Esmeraldas</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>kit 2 blusa feminina baby look academia feminina blusinha feminina casual*1</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>27.36</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:38:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3320074650698</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>(RBN INT) HENRIQUE JUNIO DO S NEVES(ESM)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Mahy</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>+5531982649692</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Avenida Jardim das Oliveiras 470 Casa, Esmeraldas</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pulseira Pedra Várias Cores Banhado A Prata 925, Delicada E Brilhant Antialérgico*1</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:38:35</t>
         </is>
       </c>
     </row>
